--- a/17 18 20/5.Power Bi/5) Dax/Data/DataCleaning.xlsx
+++ b/17 18 20/5.Power Bi/5) Dax/Data/DataCleaning.xlsx
@@ -15,11 +15,11 @@
     <sheet name="MovingAverage" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$N$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$O$16</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId7"/>
+    <pivotCache cacheId="4" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="111">
   <si>
     <t>Customer ID</t>
   </si>
@@ -236,63 +236,21 @@
     <t>lucas.t@email.com</t>
   </si>
   <si>
-    <t>C016</t>
-  </si>
-  <si>
-    <t>Cabinet</t>
-  </si>
-  <si>
-    <t>isabella.g@email.com</t>
-  </si>
-  <si>
-    <t>C017</t>
-  </si>
-  <si>
     <t>Boston-MA</t>
   </si>
   <si>
-    <t>Tablet</t>
-  </si>
-  <si>
-    <t>ethan.m@email.com</t>
-  </si>
-  <si>
-    <t>C018</t>
-  </si>
-  <si>
     <t>Miami-FL</t>
   </si>
   <si>
     <t>Calculator</t>
   </si>
   <si>
-    <t>ava.r@email.com</t>
-  </si>
-  <si>
-    <t>C019</t>
-  </si>
-  <si>
     <t>Portland-OR</t>
   </si>
   <si>
-    <t>Stool</t>
-  </si>
-  <si>
-    <t>noah.c@email.com</t>
-  </si>
-  <si>
-    <t>C020</t>
-  </si>
-  <si>
     <t>Atlanta-GA</t>
   </si>
   <si>
-    <t>Webcam</t>
-  </si>
-  <si>
-    <t>charlotte.l@email.com</t>
-  </si>
-  <si>
     <t>First Name</t>
   </si>
   <si>
@@ -368,36 +326,6 @@
     <t>Malhotra</t>
   </si>
   <si>
-    <t>Riya</t>
-  </si>
-  <si>
-    <t>Patil</t>
-  </si>
-  <si>
-    <t>Yash</t>
-  </si>
-  <si>
-    <t>Tanvi</t>
-  </si>
-  <si>
-    <t>Choudhury</t>
-  </si>
-  <si>
-    <t>Vihaan</t>
-  </si>
-  <si>
-    <t>Shinde</t>
-  </si>
-  <si>
-    <t>Pooja</t>
-  </si>
-  <si>
-    <t>Bhat</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
     <t>App 24</t>
   </si>
   <si>
@@ -429,6 +357,12 @@
   </si>
   <si>
     <t>East</t>
+  </si>
+  <si>
+    <t>Ord_Date</t>
+  </si>
+  <si>
+    <t>Ord_Date_T</t>
   </si>
 </sst>
 </file>
@@ -439,7 +373,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,6 +423,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -528,7 +470,7 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -563,6 +505,12 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -963,7 +911,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -1093,7 +1041,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -1223,7 +1171,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -1353,7 +1301,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -1483,7 +1431,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -1875,976 +1823,1038 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="9">
+        <v>46143</v>
+      </c>
+      <c r="C2" s="17">
+        <v>46143.362696759257</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="4">
+        <v>100</v>
+      </c>
+      <c r="K2" s="4">
+        <v>100</v>
+      </c>
+      <c r="L2" s="6">
+        <v>450</v>
+      </c>
+      <c r="M2" s="6">
+        <v>80</v>
+      </c>
+      <c r="N2" s="4">
+        <v>9876543210</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="9">
+        <v>46153</v>
+      </c>
+      <c r="C3" s="17">
+        <v>46153.602696759262</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="4">
+        <v>110</v>
+      </c>
+      <c r="K3" s="4">
+        <v>110</v>
+      </c>
+      <c r="L3" s="6">
+        <v>1200</v>
+      </c>
+      <c r="M3" s="6">
+        <v>250</v>
+      </c>
+      <c r="N3" s="4">
+        <v>9876543211</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="9">
+        <v>46163</v>
+      </c>
+      <c r="C4" s="17">
+        <v>46163.427499999998</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="4">
+        <v>120</v>
+      </c>
+      <c r="K4" s="4">
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <v>45</v>
+      </c>
+      <c r="M4" s="6">
+        <v>10</v>
+      </c>
+      <c r="N4" s="4">
+        <v>9876543212</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="9">
+        <v>46173</v>
+      </c>
+      <c r="C5" s="17">
+        <v>46173.825243055559</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="4">
+        <v>130</v>
+      </c>
+      <c r="K5" s="4">
+        <v>140</v>
+      </c>
+      <c r="L5" s="6">
+        <v>600</v>
+      </c>
+      <c r="M5" s="6">
+        <v>90</v>
+      </c>
+      <c r="N5" s="4">
+        <v>9876543213</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="9">
+        <v>46183</v>
+      </c>
+      <c r="C6" s="17">
+        <v>46183.315104166664</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="4">
+        <v>140</v>
+      </c>
+      <c r="K6" s="4">
+        <v>140</v>
+      </c>
+      <c r="L6" s="6">
+        <v>320</v>
+      </c>
+      <c r="M6" s="6">
+        <v>50</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="9">
+        <v>46193</v>
+      </c>
+      <c r="C7" s="17">
+        <v>46193.702870370369</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="4">
+        <v>150</v>
+      </c>
+      <c r="K7" s="4">
+        <v>150</v>
+      </c>
+      <c r="L7" s="6">
+        <v>25</v>
+      </c>
+      <c r="M7" s="6">
+        <v>5</v>
+      </c>
+      <c r="N7" s="4">
+        <v>9876543215</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="9">
+        <v>46203</v>
+      </c>
+      <c r="C8" s="17">
+        <v>46203.462835648148</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="4">
+        <v>160</v>
+      </c>
+      <c r="K8" s="4">
+        <v>160</v>
+      </c>
+      <c r="L8" s="6">
+        <v>950</v>
+      </c>
+      <c r="M8" s="6">
+        <v>180</v>
+      </c>
+      <c r="N8" s="4">
+        <v>9876543216</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46213</v>
+      </c>
+      <c r="C9" s="17">
+        <v>46213.887430555558</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F9" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="4">
+        <v>170</v>
+      </c>
+      <c r="K9" s="4">
+        <v>180</v>
+      </c>
+      <c r="L9" s="6">
+        <v>380</v>
+      </c>
+      <c r="M9" s="6">
+        <v>70</v>
+      </c>
+      <c r="N9" s="4">
+        <v>9876543217</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="9">
+        <v>46223</v>
+      </c>
+      <c r="C10" s="17">
+        <v>46223.40152777778</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="E10" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="4">
+        <v>180</v>
+      </c>
+      <c r="K10" s="4">
+        <v>180</v>
+      </c>
+      <c r="L10" s="6">
+        <v>35</v>
+      </c>
+      <c r="M10" s="6">
+        <v>8</v>
+      </c>
+      <c r="N10" s="4">
+        <v>9876543218</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="9">
+        <v>46233</v>
+      </c>
+      <c r="C11" s="17">
+        <v>46233.573344907411</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="4">
+        <v>190</v>
+      </c>
+      <c r="K11" s="4">
+        <v>190</v>
+      </c>
+      <c r="L11" s="6">
+        <v>500</v>
+      </c>
+      <c r="M11" s="6">
+        <v>100</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="9">
+        <v>46243</v>
+      </c>
+      <c r="C12" s="17">
+        <v>46243.768530092595</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12" s="4">
+        <v>200</v>
+      </c>
+      <c r="K12" s="4">
+        <v>200</v>
+      </c>
+      <c r="L12" s="6">
+        <v>75</v>
+      </c>
+      <c r="M12" s="6">
+        <v>18</v>
+      </c>
+      <c r="N12" s="4">
+        <v>9876543220</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="9">
+        <v>46253</v>
+      </c>
+      <c r="C13" s="17">
+        <v>46253.287766203706</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="4">
+        <v>210</v>
+      </c>
+      <c r="K13" s="4">
+        <v>210</v>
+      </c>
+      <c r="L13" s="6">
+        <v>40</v>
+      </c>
+      <c r="M13" s="6">
+        <v>9</v>
+      </c>
+      <c r="N13" s="4">
+        <v>9876543221</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="9">
+        <v>46263</v>
+      </c>
+      <c r="C14" s="17">
+        <v>46263.638749999998</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J14" s="4">
+        <v>220</v>
+      </c>
+      <c r="K14" s="4">
+        <v>220</v>
+      </c>
+      <c r="L14" s="6">
+        <v>700</v>
+      </c>
+      <c r="M14" s="6">
+        <v>130</v>
+      </c>
+      <c r="N14" s="4">
+        <v>9876543222</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="9">
+        <v>46273</v>
+      </c>
+      <c r="C15" s="17">
+        <v>46273.505266203705</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="J15" s="4">
+        <v>230</v>
+      </c>
+      <c r="K15" s="4">
+        <v>240</v>
+      </c>
+      <c r="L15" s="6">
+        <v>30</v>
+      </c>
+      <c r="M15" s="6">
         <v>6</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="9">
-        <v>46233</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="N15" s="4">
+        <v>9876543223</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="9">
+        <v>46283</v>
+      </c>
+      <c r="C16" s="17">
+        <v>46283.861990740741</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2" s="4">
-        <v>190</v>
-      </c>
-      <c r="J2" s="4">
-        <v>190</v>
-      </c>
-      <c r="K2" s="6">
-        <v>500</v>
-      </c>
-      <c r="L2" s="6">
-        <v>100</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="9">
-        <v>46293</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="4">
-        <v>250</v>
-      </c>
-      <c r="J3" s="4">
-        <v>250</v>
-      </c>
-      <c r="K3" s="6">
-        <v>850</v>
-      </c>
-      <c r="L3" s="6">
-        <v>160</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="7" t="s">
+      <c r="H16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="9">
-        <v>46263</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="4">
-        <v>220</v>
-      </c>
-      <c r="J4" s="4">
-        <v>220</v>
-      </c>
-      <c r="K4" s="6">
-        <v>700</v>
-      </c>
-      <c r="L4" s="6">
-        <v>130</v>
-      </c>
-      <c r="M4" s="4">
-        <v>9876543222</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="9">
-        <v>46143</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="4">
-        <v>100</v>
-      </c>
-      <c r="J5" s="4">
-        <v>100</v>
-      </c>
-      <c r="K5" s="6">
-        <v>450</v>
-      </c>
-      <c r="L5" s="6">
-        <v>80</v>
-      </c>
-      <c r="M5" s="4">
-        <v>9876543210</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="9">
-        <v>46203</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="4">
-        <v>160</v>
-      </c>
-      <c r="J6" s="4">
-        <v>160</v>
-      </c>
-      <c r="K6" s="6">
-        <v>950</v>
-      </c>
-      <c r="L6" s="6">
-        <v>180</v>
-      </c>
-      <c r="M6" s="4">
-        <v>9876543216</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="9">
-        <v>46323</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="I7" s="4">
-        <v>280</v>
-      </c>
-      <c r="J7" s="4">
-        <v>280</v>
-      </c>
-      <c r="K7" s="6">
-        <v>120</v>
-      </c>
-      <c r="L7" s="6">
-        <v>-15</v>
-      </c>
-      <c r="M7" s="4">
-        <v>9876543228</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="9">
-        <v>46173</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="4">
-        <v>130</v>
-      </c>
-      <c r="J8" s="4">
-        <v>140</v>
-      </c>
-      <c r="K8" s="6">
-        <v>600</v>
-      </c>
-      <c r="L8" s="6">
-        <v>90</v>
-      </c>
-      <c r="M8" s="4">
-        <v>9876543213</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="9">
-        <v>46313</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I9" s="4">
-        <v>270</v>
-      </c>
-      <c r="J9" s="4">
-        <v>280</v>
-      </c>
-      <c r="K9" s="6">
-        <v>55</v>
-      </c>
-      <c r="L9" s="6">
-        <v>12</v>
-      </c>
-      <c r="M9" s="4">
-        <v>9876543227</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="9">
-        <v>46283</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" s="4">
+      <c r="J16" s="4">
         <v>240</v>
       </c>
-      <c r="J10" s="4">
+      <c r="K16" s="4">
         <v>240</v>
-      </c>
-      <c r="K10" s="6">
-        <v>18</v>
-      </c>
-      <c r="L10" s="6">
-        <v>4</v>
-      </c>
-      <c r="M10" s="4">
-        <v>9876543224</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="9">
-        <v>46213</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I11" s="4">
-        <v>170</v>
-      </c>
-      <c r="J11" s="4">
-        <v>180</v>
-      </c>
-      <c r="K11" s="6">
-        <v>380</v>
-      </c>
-      <c r="L11" s="6">
-        <v>70</v>
-      </c>
-      <c r="M11" s="4">
-        <v>9876543217</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="9">
-        <v>46253</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I12" s="4">
-        <v>210</v>
-      </c>
-      <c r="J12" s="4">
-        <v>210</v>
-      </c>
-      <c r="K12" s="6">
-        <v>40</v>
-      </c>
-      <c r="L12" s="6">
-        <v>9</v>
-      </c>
-      <c r="M12" s="4">
-        <v>9876543221</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="9">
-        <v>46163</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="4">
-        <v>120</v>
-      </c>
-      <c r="J13" s="4">
-        <v>120</v>
-      </c>
-      <c r="K13" s="6">
-        <v>45</v>
-      </c>
-      <c r="L13" s="6">
-        <v>10</v>
-      </c>
-      <c r="M13" s="4">
-        <v>9876543212</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="9">
-        <v>46193</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="4">
-        <v>150</v>
-      </c>
-      <c r="J14" s="4">
-        <v>150</v>
-      </c>
-      <c r="K14" s="6">
-        <v>25</v>
-      </c>
-      <c r="L14" s="6">
-        <v>5</v>
-      </c>
-      <c r="M14" s="4">
-        <v>9876543215</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="9">
-        <v>46223</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="4">
-        <v>180</v>
-      </c>
-      <c r="J15" s="4">
-        <v>180</v>
-      </c>
-      <c r="K15" s="6">
-        <v>35</v>
-      </c>
-      <c r="L15" s="6">
-        <v>8</v>
-      </c>
-      <c r="M15" s="4">
-        <v>9876543218</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="9">
-        <v>46243</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" s="4">
-        <v>200</v>
-      </c>
-      <c r="J16" s="4">
-        <v>200</v>
-      </c>
-      <c r="K16" s="6">
-        <v>75</v>
       </c>
       <c r="L16" s="6">
         <v>18</v>
       </c>
-      <c r="M16" s="4">
+      <c r="M16" s="6">
+        <v>4</v>
+      </c>
+      <c r="N16" s="4">
+        <v>9876543224</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="9">
+        <v>46243</v>
+      </c>
+      <c r="C17" s="17">
+        <v>46243.393657407411</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="4">
+        <v>200</v>
+      </c>
+      <c r="K17" s="4">
+        <v>200</v>
+      </c>
+      <c r="L17" s="6">
+        <v>75</v>
+      </c>
+      <c r="M17" s="6">
+        <v>18</v>
+      </c>
+      <c r="N17" s="4">
         <v>9876543220</v>
       </c>
-      <c r="N16" s="7" t="s">
+      <c r="O17" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="9">
-        <v>46153</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" s="5" t="s">
+    <row r="18" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="9">
+        <v>46253</v>
+      </c>
+      <c r="C18" s="17">
+        <v>46253.734884259262</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="F18" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J18" s="4">
+        <v>210</v>
+      </c>
+      <c r="K18" s="4">
+        <v>210</v>
+      </c>
+      <c r="L18" s="6">
+        <v>40</v>
+      </c>
+      <c r="M18" s="6">
+        <v>9</v>
+      </c>
+      <c r="N18" s="4">
+        <v>9876543221</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="9">
+        <v>46263</v>
+      </c>
+      <c r="C19" s="17">
+        <v>46263.341516203705</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="4">
+        <v>220</v>
+      </c>
+      <c r="K19" s="4">
+        <v>220</v>
+      </c>
+      <c r="L19" s="6">
+        <v>700</v>
+      </c>
+      <c r="M19" s="6">
+        <v>130</v>
+      </c>
+      <c r="N19" s="4">
+        <v>9876543222</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="9">
+        <v>46273</v>
+      </c>
+      <c r="C20" s="17">
+        <v>46273.622557870367</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="4">
-        <v>110</v>
-      </c>
-      <c r="J17" s="4">
-        <v>110</v>
-      </c>
-      <c r="K17" s="6">
-        <v>1200</v>
-      </c>
-      <c r="L17" s="6">
-        <v>250</v>
-      </c>
-      <c r="M17" s="4">
-        <v>9876543211</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="9">
-        <v>46273</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="4" t="s">
+      <c r="I20" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="I18" s="4">
+      <c r="J20" s="4">
         <v>230</v>
       </c>
-      <c r="J18" s="4">
+      <c r="K20" s="4">
         <v>240</v>
       </c>
-      <c r="K18" s="6">
+      <c r="L20" s="6">
         <v>30</v>
       </c>
-      <c r="L18" s="6">
+      <c r="M20" s="6">
         <v>6</v>
       </c>
-      <c r="M18" s="4">
+      <c r="N20" s="4">
         <v>9876543223</v>
       </c>
-      <c r="N18" s="8" t="s">
+      <c r="O20" s="8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="9">
-        <v>46183</v>
-      </c>
-      <c r="C19" s="5" t="s">
+    <row r="21" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="9">
+        <v>46283</v>
+      </c>
+      <c r="C21" s="17">
+        <v>46283.475034722222</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I19" s="4">
-        <v>140</v>
-      </c>
-      <c r="J19" s="4">
-        <v>140</v>
-      </c>
-      <c r="K19" s="6">
-        <v>320</v>
-      </c>
-      <c r="L19" s="6">
-        <v>50</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="9">
-        <v>46303</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I20" s="4">
-        <v>260</v>
-      </c>
-      <c r="J20" s="4">
-        <v>260</v>
-      </c>
-      <c r="K20" s="6">
-        <v>650</v>
-      </c>
-      <c r="L20" s="6">
-        <v>140</v>
-      </c>
-      <c r="M20" s="4">
-        <v>9876543226</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="9">
-        <v>46333</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="E21" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>84</v>
+        <v>97</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="I21" s="4">
-        <v>290</v>
+        <v>20</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="J21" s="4">
-        <v>290</v>
-      </c>
-      <c r="K21" s="6">
-        <v>95</v>
+        <v>240</v>
+      </c>
+      <c r="K21" s="4">
+        <v>240</v>
       </c>
       <c r="L21" s="6">
-        <v>20</v>
-      </c>
-      <c r="M21" s="4">
-        <v>9876543229</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>86</v>
+        <v>18</v>
+      </c>
+      <c r="M21" s="6">
+        <v>4</v>
+      </c>
+      <c r="N21" s="4">
+        <v>9876543224</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N21">
+  <autoFilter ref="A1:O16">
     <sortState ref="A2:N21">
-      <sortCondition ref="G2:G21"/>
-      <sortCondition ref="H2:H21"/>
+      <sortCondition ref="A2:A21"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="N5" r:id="rId1" display="mailto:john.smith@email.com"/>
-    <hyperlink ref="N17" r:id="rId2" display="mailto:emily.j@email.com"/>
-    <hyperlink ref="N13" r:id="rId3" display="mailto:michael.b@email.com"/>
-    <hyperlink ref="N8" r:id="rId4" display="mailto:sarah.d@email.com"/>
-    <hyperlink ref="N19" r:id="rId5" display="mailto:david.w@email.com"/>
-    <hyperlink ref="N6" r:id="rId6" display="mailto:daniel.m@email.com"/>
-    <hyperlink ref="N11" r:id="rId7" display="mailto:ashley.t@email.com"/>
-    <hyperlink ref="N15" r:id="rId8" display="mailto:james.a@email.com"/>
-    <hyperlink ref="N2" r:id="rId9" display="mailto:olivia.t@email.com"/>
-    <hyperlink ref="N16" r:id="rId10" display="mailto:william.j@email.com"/>
-    <hyperlink ref="N12" r:id="rId11" display="mailto:sophia.w@email.com"/>
-    <hyperlink ref="N4" r:id="rId12" display="mailto:ben.h@email.com"/>
-    <hyperlink ref="N10" r:id="rId13" display="mailto:lucas.t@email.com"/>
-    <hyperlink ref="N3" r:id="rId14" display="mailto:isabella.g@email.com"/>
-    <hyperlink ref="N20" r:id="rId15" display="mailto:ethan.m@email.com"/>
-    <hyperlink ref="N9" r:id="rId16" display="mailto:ava.r@email.com"/>
-    <hyperlink ref="N7" r:id="rId17" display="mailto:noah.c@email.com"/>
-    <hyperlink ref="N21" r:id="rId18" display="mailto:charlotte.l@email.com"/>
+    <hyperlink ref="O2" r:id="rId1" display="mailto:john.smith@email.com"/>
+    <hyperlink ref="O3" r:id="rId2" display="mailto:emily.j@email.com"/>
+    <hyperlink ref="O4" r:id="rId3" display="mailto:michael.b@email.com"/>
+    <hyperlink ref="O5" r:id="rId4" display="mailto:sarah.d@email.com"/>
+    <hyperlink ref="O6" r:id="rId5" display="mailto:david.w@email.com"/>
+    <hyperlink ref="O8" r:id="rId6" display="mailto:daniel.m@email.com"/>
+    <hyperlink ref="O9" r:id="rId7" display="mailto:ashley.t@email.com"/>
+    <hyperlink ref="O10" r:id="rId8" display="mailto:james.a@email.com"/>
+    <hyperlink ref="O11" r:id="rId9" display="mailto:olivia.t@email.com"/>
+    <hyperlink ref="O12" r:id="rId10" display="mailto:william.j@email.com"/>
+    <hyperlink ref="O13" r:id="rId11" display="mailto:sophia.w@email.com"/>
+    <hyperlink ref="O14" r:id="rId12" display="mailto:ben.h@email.com"/>
+    <hyperlink ref="O16" r:id="rId13" display="mailto:lucas.t@email.com"/>
+    <hyperlink ref="O17" r:id="rId14" display="mailto:william.j@email.com"/>
+    <hyperlink ref="O18" r:id="rId15" display="mailto:sophia.w@email.com"/>
+    <hyperlink ref="O19" r:id="rId16" display="mailto:ben.h@email.com"/>
+    <hyperlink ref="O21" r:id="rId17" display="mailto:lucas.t@email.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2863,13 +2873,13 @@
   <sheetData>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2938,7 +2948,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B9" s="12">
         <v>55</v>
@@ -2964,7 +2974,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B11" s="12">
         <v>95</v>
@@ -2977,7 +2987,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B12" s="12">
         <v>120</v>
@@ -3055,7 +3065,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B18" s="12">
         <v>650</v>
@@ -3120,7 +3130,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B23" s="12">
         <v>7138</v>
@@ -3144,10 +3154,10 @@
   <sheetData>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -3212,7 +3222,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B9" s="12">
         <v>55</v>
@@ -3238,7 +3248,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B11" s="12">
         <v>95</v>
@@ -3251,7 +3261,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B12" s="12">
         <v>120</v>
@@ -3329,7 +3339,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B18" s="12">
         <v>650</v>
@@ -3394,7 +3404,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B23" s="12">
         <v>7138</v>
@@ -3418,10 +3428,10 @@
   <sheetData>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -3490,7 +3500,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B9" s="12">
         <v>55</v>
@@ -3516,7 +3526,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B11" s="12">
         <v>95</v>
@@ -3529,7 +3539,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B12" s="12">
         <v>120</v>
@@ -3607,7 +3617,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B18" s="12">
         <v>650</v>
@@ -3672,7 +3682,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B23" s="12">
         <v>7138</v>
@@ -3699,10 +3709,10 @@
   <sheetData>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="G3">
         <v>25</v>
@@ -3777,7 +3787,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B9" s="12">
         <v>55</v>
@@ -3801,7 +3811,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B11" s="12">
         <v>95</v>
@@ -3813,7 +3823,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B12" s="12">
         <v>120</v>
@@ -3885,7 +3895,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B18" s="12">
         <v>650</v>
@@ -3945,7 +3955,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B23" s="12">
         <v>7138</v>
@@ -3968,10 +3978,10 @@
   <sheetData>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -4071,7 +4081,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B9" s="12">
         <v>55</v>
@@ -4109,7 +4119,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B11" s="12">
         <v>95</v>
@@ -4128,7 +4138,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B12" s="12">
         <v>120</v>
@@ -4242,7 +4252,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B18" s="12">
         <v>650</v>
@@ -4337,7 +4347,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B23" s="12">
         <v>7138</v>
